--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/110.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/110.xlsx
@@ -426,13 +426,13 @@
         <v>-24.17131184523438</v>
       </c>
       <c r="E2">
-        <v>-15.14650230201284</v>
+        <v>-11.49394837927612</v>
       </c>
       <c r="F2">
-        <v>-2.818376927712141</v>
+        <v>-2.586374412475278</v>
       </c>
       <c r="G2">
-        <v>-11.89683387986744</v>
+        <v>-9.735964663837732</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-24.38873788833369</v>
       </c>
       <c r="E3">
-        <v>-17.05665792318827</v>
+        <v>-13.32036798757572</v>
       </c>
       <c r="F3">
-        <v>-3.240647151698023</v>
+        <v>-2.671279586160019</v>
       </c>
       <c r="G3">
-        <v>-12.48325398505732</v>
+        <v>-9.399381498860031</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-24.48622667205209</v>
       </c>
       <c r="E4">
-        <v>-15.72795836459771</v>
+        <v>-12.56091572564535</v>
       </c>
       <c r="F4">
-        <v>-3.161329316145165</v>
+        <v>-2.623958269907694</v>
       </c>
       <c r="G4">
-        <v>-11.18782096281281</v>
+        <v>-9.252462798372715</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-24.40502338662245</v>
       </c>
       <c r="E5">
-        <v>-17.7291815980674</v>
+        <v>-12.58664651495694</v>
       </c>
       <c r="F5">
-        <v>-3.07779012030764</v>
+        <v>-2.459738574139707</v>
       </c>
       <c r="G5">
-        <v>-11.3390201986824</v>
+        <v>-9.611994665028645</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-24.11463798313046</v>
       </c>
       <c r="E6">
-        <v>-17.14991731690224</v>
+        <v>-14.64970153252735</v>
       </c>
       <c r="F6">
-        <v>-3.554339946729362</v>
+        <v>-2.15757168315092</v>
       </c>
       <c r="G6">
-        <v>-11.45071138408633</v>
+        <v>-9.601947159316955</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-23.61857550995557</v>
       </c>
       <c r="E7">
-        <v>-17.80925407547102</v>
+        <v>-14.57631761123306</v>
       </c>
       <c r="F7">
-        <v>-3.039966864695815</v>
+        <v>-2.042880902763717</v>
       </c>
       <c r="G7">
-        <v>-10.68292966261856</v>
+        <v>-9.00088120066134</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-22.93216845818666</v>
       </c>
       <c r="E8">
-        <v>-18.45012824551054</v>
+        <v>-15.20170892864035</v>
       </c>
       <c r="F8">
-        <v>-2.863371359930002</v>
+        <v>-1.939561121714743</v>
       </c>
       <c r="G8">
-        <v>-11.38174609941223</v>
+        <v>-8.632976964336594</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-22.05315702444173</v>
       </c>
       <c r="E9">
-        <v>-18.36669564039322</v>
+        <v>-14.99005711046985</v>
       </c>
       <c r="F9">
-        <v>-3.251125170976034</v>
+        <v>-2.496422824572682</v>
       </c>
       <c r="G9">
-        <v>-11.08687911877489</v>
+        <v>-9.420376978670088</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-21.00483474580345</v>
       </c>
       <c r="E10">
-        <v>-18.69109740440669</v>
+        <v>-16.44199003223114</v>
       </c>
       <c r="F10">
-        <v>-2.790834539936461</v>
+        <v>-2.487389478045154</v>
       </c>
       <c r="G10">
-        <v>-9.893973691881607</v>
+        <v>-8.187721831486776</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-19.83522688460056</v>
       </c>
       <c r="E11">
-        <v>-20.03498999329299</v>
+        <v>-16.28773662210787</v>
       </c>
       <c r="F11">
-        <v>-2.943095923877635</v>
+        <v>-2.033874063993078</v>
       </c>
       <c r="G11">
-        <v>-10.35343768618598</v>
+        <v>-8.095188773118608</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-18.57628922196349</v>
       </c>
       <c r="E12">
-        <v>-20.98218373063335</v>
+        <v>-16.92905911107414</v>
       </c>
       <c r="F12">
-        <v>-2.00636812438312</v>
+        <v>-2.752836498802644</v>
       </c>
       <c r="G12">
-        <v>-9.573281145492407</v>
+        <v>-7.629779039025706</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-17.25360268518005</v>
       </c>
       <c r="E13">
-        <v>-19.97161399955564</v>
+        <v>-17.54119558506099</v>
       </c>
       <c r="F13">
-        <v>-2.491792250791034</v>
+        <v>-1.976049049073256</v>
       </c>
       <c r="G13">
-        <v>-8.881605555426939</v>
+        <v>-7.586450619007725</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.93795261756844</v>
       </c>
       <c r="E14">
-        <v>-21.41879655208289</v>
+        <v>-18.02691065017569</v>
       </c>
       <c r="F14">
-        <v>-2.498835030449635</v>
+        <v>-1.974673130817206</v>
       </c>
       <c r="G14">
-        <v>-9.376161332447582</v>
+        <v>-7.14518138298719</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.6713577934795</v>
       </c>
       <c r="E15">
-        <v>-22.56322797482733</v>
+        <v>-17.75650641022968</v>
       </c>
       <c r="F15">
-        <v>-2.872301160532181</v>
+        <v>-2.028996636725394</v>
       </c>
       <c r="G15">
-        <v>-8.253240838254492</v>
+        <v>-6.589910200776313</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.47664723792204</v>
       </c>
       <c r="E16">
-        <v>-23.75144068427794</v>
+        <v>-19.93129246699134</v>
       </c>
       <c r="F16">
-        <v>-2.394731613837612</v>
+        <v>-1.924746599083077</v>
       </c>
       <c r="G16">
-        <v>-9.132359516753496</v>
+        <v>-5.771894261295638</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.4069507997562</v>
       </c>
       <c r="E17">
-        <v>-23.20954989909808</v>
+        <v>-20.32049216558057</v>
       </c>
       <c r="F17">
-        <v>-3.06208096088095</v>
+        <v>-2.084498081080364</v>
       </c>
       <c r="G17">
-        <v>-7.519233302378363</v>
+        <v>-5.1270496484287</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.48875877741321</v>
       </c>
       <c r="E18">
-        <v>-23.87696545529655</v>
+        <v>-21.08028406306152</v>
       </c>
       <c r="F18">
-        <v>-2.204695847961378</v>
+        <v>-1.905116776738937</v>
       </c>
       <c r="G18">
-        <v>-6.544804017803743</v>
+        <v>-4.976499279484804</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.71746002974362</v>
       </c>
       <c r="E19">
-        <v>-23.96402536809401</v>
+        <v>-20.54649924635539</v>
       </c>
       <c r="F19">
-        <v>-2.491262924020644</v>
+        <v>-2.102748671698843</v>
       </c>
       <c r="G19">
-        <v>-6.780448649289066</v>
+        <v>-4.614997638233008</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.10747536699702</v>
       </c>
       <c r="E20">
-        <v>-25.70722520955466</v>
+        <v>-22.12245348576475</v>
       </c>
       <c r="F20">
-        <v>-2.184038850037767</v>
+        <v>-1.310022604772189</v>
       </c>
       <c r="G20">
-        <v>-6.51856132331394</v>
+        <v>-4.003281654577556</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.665601425903215</v>
       </c>
       <c r="E21">
-        <v>-25.98526898515161</v>
+        <v>-22.25458530036055</v>
       </c>
       <c r="F21">
-        <v>-1.987295793301064</v>
+        <v>-1.515009573901552</v>
       </c>
       <c r="G21">
-        <v>-6.985321759986864</v>
+        <v>-4.406880192906725</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.372956330064509</v>
       </c>
       <c r="E22">
-        <v>-25.62279634015565</v>
+        <v>-24.13525149879804</v>
       </c>
       <c r="F22">
-        <v>-1.870365107456692</v>
+        <v>-1.339568813295241</v>
       </c>
       <c r="G22">
-        <v>-5.087783267787405</v>
+        <v>-3.084118617235529</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.213493480061938</v>
       </c>
       <c r="E23">
-        <v>-26.03787173922471</v>
+        <v>-23.43840086154971</v>
       </c>
       <c r="F23">
-        <v>-2.131524498537292</v>
+        <v>-1.014781693638209</v>
       </c>
       <c r="G23">
-        <v>-6.486101424301386</v>
+        <v>-3.537424996836854</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.182434121888663</v>
       </c>
       <c r="E24">
-        <v>-28.50161519394181</v>
+        <v>-22.99960984410248</v>
       </c>
       <c r="F24">
-        <v>-1.246104119237373</v>
+        <v>-0.8047309145755323</v>
       </c>
       <c r="G24">
-        <v>-5.837307330606097</v>
+        <v>-4.285499040709346</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.250362439396433</v>
       </c>
       <c r="E25">
-        <v>-28.83354328175603</v>
+        <v>-25.16971798721422</v>
       </c>
       <c r="F25">
-        <v>-1.883299236084003</v>
+        <v>-1.091413133703788</v>
       </c>
       <c r="G25">
-        <v>-4.877186223852207</v>
+        <v>-3.642786419169699</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.379249511836237</v>
       </c>
       <c r="E26">
-        <v>-29.1366883887775</v>
+        <v>-25.98477085301077</v>
       </c>
       <c r="F26">
-        <v>-1.278881788998747</v>
+        <v>-0.6245991093671686</v>
       </c>
       <c r="G26">
-        <v>-4.843809303725275</v>
+        <v>-3.974797720757667</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.560129201417356</v>
       </c>
       <c r="E27">
-        <v>-27.69019416429942</v>
+        <v>-26.23259159308052</v>
       </c>
       <c r="F27">
-        <v>-1.863728227825462</v>
+        <v>-0.3599705156036441</v>
       </c>
       <c r="G27">
-        <v>-6.805082418646783</v>
+        <v>-4.63610898713694</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.767452160006243</v>
       </c>
       <c r="E28">
-        <v>-30.36660381536474</v>
+        <v>-25.40323780636776</v>
       </c>
       <c r="F28">
-        <v>-1.660202498794638</v>
+        <v>-0.7868373503076601</v>
       </c>
       <c r="G28">
-        <v>-6.343244763190756</v>
+        <v>-4.222466253641623</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.968061627544591</v>
       </c>
       <c r="E29">
-        <v>-27.09140763168719</v>
+        <v>-26.02828948822448</v>
       </c>
       <c r="F29">
-        <v>-2.172662880495121</v>
+        <v>-0.6401906406226608</v>
       </c>
       <c r="G29">
-        <v>-5.341589552101169</v>
+        <v>-3.966763026733856</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.15896717735827</v>
       </c>
       <c r="E30">
-        <v>-27.95081690038887</v>
+        <v>-25.87413117605536</v>
       </c>
       <c r="F30">
-        <v>-1.123801470785846</v>
+        <v>-0.9342271055529706</v>
       </c>
       <c r="G30">
-        <v>-6.559529324362421</v>
+        <v>-4.628246441481171</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.33216218489496</v>
       </c>
       <c r="E31">
-        <v>-27.84432530562449</v>
+        <v>-24.91287199844718</v>
       </c>
       <c r="F31">
-        <v>-1.076415541876103</v>
+        <v>-0.8268317568822231</v>
       </c>
       <c r="G31">
-        <v>-7.637966018144325</v>
+        <v>-4.624882927213271</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.46978729012757</v>
       </c>
       <c r="E32">
-        <v>-29.77266274994072</v>
+        <v>-25.17785565500601</v>
       </c>
       <c r="F32">
-        <v>-1.674464500368637</v>
+        <v>-0.4618737883938309</v>
       </c>
       <c r="G32">
-        <v>-5.957079557671389</v>
+        <v>-4.451608973687818</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.5760900608382</v>
       </c>
       <c r="E33">
-        <v>-27.16882189484832</v>
+        <v>-25.71715162457947</v>
       </c>
       <c r="F33">
-        <v>-1.741070209758134</v>
+        <v>-0.2897216463766348</v>
       </c>
       <c r="G33">
-        <v>-5.527148940122858</v>
+        <v>-4.75189200682741</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.6581552726261</v>
       </c>
       <c r="E34">
-        <v>-29.1409994960328</v>
+        <v>-24.67389083964039</v>
       </c>
       <c r="F34">
-        <v>-1.720770238185129</v>
+        <v>-0.3952863030871954</v>
       </c>
       <c r="G34">
-        <v>-6.151478102282933</v>
+        <v>-3.938047354726217</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.7118403321452</v>
       </c>
       <c r="E35">
-        <v>-28.77668376211572</v>
+        <v>-24.61118053158217</v>
       </c>
       <c r="F35">
-        <v>-1.395316282768843</v>
+        <v>-0.2513607803203926</v>
       </c>
       <c r="G35">
-        <v>-6.796455136971442</v>
+        <v>-5.183938062975536</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.73834872229591</v>
       </c>
       <c r="E36">
-        <v>-29.16474228525502</v>
+        <v>-24.97477623813203</v>
       </c>
       <c r="F36">
-        <v>-1.249116063113952</v>
+        <v>-0.3628532341653864</v>
       </c>
       <c r="G36">
-        <v>-6.87622935283126</v>
+        <v>-5.552011137122785</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.75102633120676</v>
       </c>
       <c r="E37">
-        <v>-27.21111784207996</v>
+        <v>-25.43449786244271</v>
       </c>
       <c r="F37">
-        <v>-0.8230444611166238</v>
+        <v>-0.04771079617914808</v>
       </c>
       <c r="G37">
-        <v>-7.134382383438088</v>
+        <v>-4.94880325550326</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.7496664817301</v>
       </c>
       <c r="E38">
-        <v>-28.15621036748076</v>
+        <v>-23.26670829802289</v>
       </c>
       <c r="F38">
-        <v>-0.9183125110103865</v>
+        <v>-0.2684773359644387</v>
       </c>
       <c r="G38">
-        <v>-5.419854159195079</v>
+        <v>-4.44959947254548</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.72714104718459</v>
       </c>
       <c r="E39">
-        <v>-26.78863838800836</v>
+        <v>-24.23379562167895</v>
       </c>
       <c r="F39">
-        <v>-1.263450132651995</v>
+        <v>-0.13167825796392</v>
       </c>
       <c r="G39">
-        <v>-6.36352847570987</v>
+        <v>-4.253535723527683</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.69734867373958</v>
       </c>
       <c r="E40">
-        <v>-26.35682122053295</v>
+        <v>-24.60563315092277</v>
       </c>
       <c r="F40">
-        <v>-0.648738563852149</v>
+        <v>-0.4312830085758479</v>
       </c>
       <c r="G40">
-        <v>-6.93268739645799</v>
+        <v>-4.843700055722479</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.66004680530835</v>
       </c>
       <c r="E41">
-        <v>-24.68753060335149</v>
+        <v>-23.35080206034533</v>
       </c>
       <c r="F41">
-        <v>-1.502829259610788</v>
+        <v>-0.1143736629194383</v>
       </c>
       <c r="G41">
-        <v>-6.599663067935006</v>
+        <v>-4.744559148457925</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.60236371128759</v>
       </c>
       <c r="E42">
-        <v>-26.27092059708145</v>
+        <v>-22.29019721995687</v>
       </c>
       <c r="F42">
-        <v>-0.8779834440050925</v>
+        <v>-0.01991161450859947</v>
       </c>
       <c r="G42">
-        <v>-6.558281248694116</v>
+        <v>-5.221704766487542</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.53288617481496</v>
       </c>
       <c r="E43">
-        <v>-23.69764694154082</v>
+        <v>-22.15221461694316</v>
       </c>
       <c r="F43">
-        <v>-0.672470461574952</v>
+        <v>-0.1696332239927905</v>
       </c>
       <c r="G43">
-        <v>-6.927678541057073</v>
+        <v>-5.402450621295131</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.45222070103172</v>
       </c>
       <c r="E44">
-        <v>-26.1120164441523</v>
+        <v>-21.89867894267572</v>
       </c>
       <c r="F44">
-        <v>-0.8562263741705636</v>
+        <v>-0.4382015331240294</v>
       </c>
       <c r="G44">
-        <v>-6.286035225726611</v>
+        <v>-4.548723827082338</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.34791696455214</v>
       </c>
       <c r="E45">
-        <v>-24.17153363254749</v>
+        <v>-20.99492685649093</v>
       </c>
       <c r="F45">
-        <v>-1.095116764361705</v>
+        <v>-0.4076140667756577</v>
       </c>
       <c r="G45">
-        <v>-7.211057928673148</v>
+        <v>-4.919302984202815</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.22309053131882</v>
       </c>
       <c r="E46">
-        <v>-22.45016103580382</v>
+        <v>-20.4277807717703</v>
       </c>
       <c r="F46">
-        <v>-1.307679153389669</v>
+        <v>-0.1017162090046618</v>
       </c>
       <c r="G46">
-        <v>-6.314870077373662</v>
+        <v>-4.382057722453269</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.08338365781654</v>
       </c>
       <c r="E47">
-        <v>-21.86203000253164</v>
+        <v>-20.65017413028699</v>
       </c>
       <c r="F47">
-        <v>-0.4158389267180539</v>
+        <v>-0.04506084885759246</v>
       </c>
       <c r="G47">
-        <v>-7.244001167334435</v>
+        <v>-4.966726549052875</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.923218514253152</v>
       </c>
       <c r="E48">
-        <v>-21.8165460095986</v>
+        <v>-20.10486434723134</v>
       </c>
       <c r="F48">
-        <v>-0.6605502546486671</v>
+        <v>-0.1210113709180707</v>
       </c>
       <c r="G48">
-        <v>-6.432265332741758</v>
+        <v>-4.644289345164479</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.741031592063898</v>
       </c>
       <c r="E49">
-        <v>-23.16942761939012</v>
+        <v>-20.31216883035448</v>
       </c>
       <c r="F49">
-        <v>-1.528364513169485</v>
+        <v>-0.1435355089675921</v>
       </c>
       <c r="G49">
-        <v>-6.259077453400325</v>
+        <v>-4.577131618354824</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.550095630932784</v>
       </c>
       <c r="E50">
-        <v>-21.25409595242392</v>
+        <v>-19.38319767242098</v>
       </c>
       <c r="F50">
-        <v>-0.8589028292490087</v>
+        <v>0.09681529295468447</v>
       </c>
       <c r="G50">
-        <v>-7.753666274196313</v>
+        <v>-4.934173954765221</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.35099488200858</v>
       </c>
       <c r="E51">
-        <v>-22.61183208635166</v>
+        <v>-20.14054419393778</v>
       </c>
       <c r="F51">
-        <v>-0.8319452688597044</v>
+        <v>0.02917329594428524</v>
       </c>
       <c r="G51">
-        <v>-8.22145629053195</v>
+        <v>-5.824128048814258</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.138063486965857</v>
       </c>
       <c r="E52">
-        <v>-20.91096441991472</v>
+        <v>-18.02493170703434</v>
       </c>
       <c r="F52">
-        <v>-0.8920681749548925</v>
+        <v>-0.04506333395980086</v>
       </c>
       <c r="G52">
-        <v>-7.183358594146066</v>
+        <v>-4.724695875222298</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.926644261074683</v>
       </c>
       <c r="E53">
-        <v>-20.64176022558074</v>
+        <v>-17.3764270582919</v>
       </c>
       <c r="F53">
-        <v>-0.5148246895155809</v>
+        <v>-0.4899479880421089</v>
       </c>
       <c r="G53">
-        <v>-7.189774431401173</v>
+        <v>-5.007975946472194</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.71982353819884</v>
       </c>
       <c r="E54">
-        <v>-20.23712295909936</v>
+        <v>-18.31179242152423</v>
       </c>
       <c r="F54">
-        <v>-0.7734948365507686</v>
+        <v>-0.5224067363534047</v>
       </c>
       <c r="G54">
-        <v>-7.901425853250604</v>
+        <v>-4.481777975187196</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.509979010025789</v>
       </c>
       <c r="E55">
-        <v>-19.28254328065249</v>
+        <v>-17.93734196277798</v>
       </c>
       <c r="F55">
-        <v>-1.011672830775502</v>
+        <v>0.04460578065844003</v>
       </c>
       <c r="G55">
-        <v>-6.790390217543497</v>
+        <v>-5.298797440460549</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.308198950400982</v>
       </c>
       <c r="E56">
-        <v>-18.80888754182021</v>
+        <v>-17.16589830167531</v>
       </c>
       <c r="F56">
-        <v>-0.6543565515779353</v>
+        <v>-0.3835773298486244</v>
       </c>
       <c r="G56">
-        <v>-8.119660325744899</v>
+        <v>-5.49984024996941</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.118902768597819</v>
       </c>
       <c r="E57">
-        <v>-20.09330768156377</v>
+        <v>-16.26427912674814</v>
       </c>
       <c r="F57">
-        <v>-1.203111851032079</v>
+        <v>-0.4718249660036614</v>
       </c>
       <c r="G57">
-        <v>-8.102134297659997</v>
+        <v>-5.807353514566771</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.93491306243062</v>
       </c>
       <c r="E58">
-        <v>-18.94749054577298</v>
+        <v>-16.65110590495734</v>
       </c>
       <c r="F58">
-        <v>-1.226987056315566</v>
+        <v>-0.3218772122185061</v>
       </c>
       <c r="G58">
-        <v>-8.693414283701529</v>
+        <v>-4.546436240114701</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.760640398649708</v>
       </c>
       <c r="E59">
-        <v>-19.04004802601575</v>
+        <v>-15.34834997395673</v>
       </c>
       <c r="F59">
-        <v>-1.166373756717921</v>
+        <v>-0.3835980390336944</v>
       </c>
       <c r="G59">
-        <v>-7.841504978989795</v>
+        <v>-5.305279488626443</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.603699570267517</v>
       </c>
       <c r="E60">
-        <v>-17.94259499262688</v>
+        <v>-16.14961816487392</v>
       </c>
       <c r="F60">
-        <v>-1.42843523990017</v>
+        <v>-0.4779755939694477</v>
       </c>
       <c r="G60">
-        <v>-7.981554297483124</v>
+        <v>-5.322606883978988</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.460541737628795</v>
       </c>
       <c r="E61">
-        <v>-18.02597778453011</v>
+        <v>-15.58171129652</v>
       </c>
       <c r="F61">
-        <v>-1.448477589210904</v>
+        <v>0.37436310473227</v>
       </c>
       <c r="G61">
-        <v>-7.176240921236633</v>
+        <v>-5.618847741015131</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.327977714587783</v>
       </c>
       <c r="E62">
-        <v>-18.46124564919937</v>
+        <v>-15.83631569065325</v>
       </c>
       <c r="F62">
-        <v>-0.5439923341355543</v>
+        <v>-0.1728613717615002</v>
       </c>
       <c r="G62">
-        <v>-8.632344650138593</v>
+        <v>-5.469687801197728</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.215421517349334</v>
       </c>
       <c r="E63">
-        <v>-18.84320884632434</v>
+        <v>-15.76260119075639</v>
       </c>
       <c r="F63">
-        <v>-0.4846630040122481</v>
+        <v>-0.4059241972739467</v>
       </c>
       <c r="G63">
-        <v>-7.885147900834007</v>
+        <v>-5.949918847669946</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.120029686148862</v>
       </c>
       <c r="E64">
-        <v>-16.85126445609637</v>
+        <v>-14.33042600109056</v>
       </c>
       <c r="F64">
-        <v>-0.8650733380324622</v>
+        <v>-0.6203487562234044</v>
       </c>
       <c r="G64">
-        <v>-7.661848293664627</v>
+        <v>-5.687180711491227</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.032775991106097</v>
       </c>
       <c r="E65">
-        <v>-16.519245798802</v>
+        <v>-14.6822023904804</v>
       </c>
       <c r="F65">
-        <v>-1.091346035944161</v>
+        <v>-0.5485823179144663</v>
       </c>
       <c r="G65">
-        <v>-7.672034842288964</v>
+        <v>-6.322183072469913</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.963128533265014</v>
       </c>
       <c r="E66">
-        <v>-17.93358785782562</v>
+        <v>-16.00758257762334</v>
       </c>
       <c r="F66">
-        <v>-1.225244171300076</v>
+        <v>-0.3406008006239833</v>
       </c>
       <c r="G66">
-        <v>-8.52393090481854</v>
+        <v>-5.224353202918959</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.911581897347307</v>
       </c>
       <c r="E67">
-        <v>-15.27179612085706</v>
+        <v>-13.75520564721425</v>
       </c>
       <c r="F67">
-        <v>-1.071050206208171</v>
+        <v>-0.6652164482286368</v>
       </c>
       <c r="G67">
-        <v>-7.74705180420885</v>
+        <v>-5.568762497551497</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.869229617542595</v>
       </c>
       <c r="E68">
-        <v>-17.97228819669517</v>
+        <v>-15.33748163633832</v>
       </c>
       <c r="F68">
-        <v>-1.28871533843738</v>
+        <v>-0.7931577935910203</v>
       </c>
       <c r="G68">
-        <v>-8.466612119351598</v>
+        <v>-5.11483042484325</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.8442495498188</v>
       </c>
       <c r="E69">
-        <v>-15.00382367145317</v>
+        <v>-13.24033626643816</v>
       </c>
       <c r="F69">
-        <v>-1.172438234473816</v>
+        <v>-0.3718054006874407</v>
       </c>
       <c r="G69">
-        <v>-8.322212744019668</v>
+        <v>-5.46577473637031</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.83988293052473</v>
       </c>
       <c r="E70">
-        <v>-16.55442751336759</v>
+        <v>-15.05586942322332</v>
       </c>
       <c r="F70">
-        <v>-1.320098037492439</v>
+        <v>-0.8934672874982209</v>
       </c>
       <c r="G70">
-        <v>-7.740516787314328</v>
+        <v>-6.224002223411747</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.848803498196893</v>
       </c>
       <c r="E71">
-        <v>-16.27170129564671</v>
+        <v>-13.85684724631641</v>
       </c>
       <c r="F71">
-        <v>-1.772634321274406</v>
+        <v>-1.007317274971582</v>
       </c>
       <c r="G71">
-        <v>-7.456839450599719</v>
+        <v>-5.692656353813182</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.872877645544469</v>
       </c>
       <c r="E72">
-        <v>-17.79606263068668</v>
+        <v>-13.57119110591257</v>
       </c>
       <c r="F72">
-        <v>-1.078015119330909</v>
+        <v>-1.155780594370921</v>
       </c>
       <c r="G72">
-        <v>-7.110791435925242</v>
+        <v>-5.370003964464733</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.916968944912911</v>
       </c>
       <c r="E73">
-        <v>-15.75277893063375</v>
+        <v>-15.22135344888562</v>
       </c>
       <c r="F73">
-        <v>-1.380362594413506</v>
+        <v>-1.1385828587214</v>
       </c>
       <c r="G73">
-        <v>-8.151560742561317</v>
+        <v>-5.496830964074213</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.975282553161399</v>
       </c>
       <c r="E74">
-        <v>-16.31716717468372</v>
+        <v>-14.52865995077633</v>
       </c>
       <c r="F74">
-        <v>-1.236183591221446</v>
+        <v>-1.406923366816869</v>
       </c>
       <c r="G74">
-        <v>-7.36267429328069</v>
+        <v>-5.890461449784635</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.041456043436091</v>
       </c>
       <c r="E75">
-        <v>-17.12262420405801</v>
+        <v>-16.62499472382912</v>
       </c>
       <c r="F75">
-        <v>-1.555142317832382</v>
+        <v>-1.302548245696729</v>
       </c>
       <c r="G75">
-        <v>-6.825998445363898</v>
+        <v>-5.256197340461208</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.121641118685804</v>
       </c>
       <c r="E76">
-        <v>-16.42811025939763</v>
+        <v>-14.37860443605817</v>
       </c>
       <c r="F76">
-        <v>-2.051163748424309</v>
+        <v>-0.9777901188987937</v>
       </c>
       <c r="G76">
-        <v>-7.84207770336809</v>
+        <v>-5.699101985978143</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.211487621679787</v>
       </c>
       <c r="E77">
-        <v>-19.89342989581321</v>
+        <v>-14.63383828807848</v>
       </c>
       <c r="F77">
-        <v>-1.866960517431186</v>
+        <v>-1.371394688910798</v>
       </c>
       <c r="G77">
-        <v>-7.551183377377869</v>
+        <v>-5.171983683033227</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.300626410614743</v>
       </c>
       <c r="E78">
-        <v>-17.79183756443753</v>
+        <v>-15.94500359531134</v>
       </c>
       <c r="F78">
-        <v>-1.962001594656582</v>
+        <v>-1.337695046230109</v>
       </c>
       <c r="G78">
-        <v>-6.45356207219589</v>
+        <v>-5.753954415018327</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.395891516261314</v>
       </c>
       <c r="E79">
-        <v>-18.74719614041372</v>
+        <v>-16.5229048058002</v>
       </c>
       <c r="F79">
-        <v>-1.760606426585757</v>
+        <v>-1.675541377992276</v>
       </c>
       <c r="G79">
-        <v>-7.260206287749168</v>
+        <v>-4.591846993276884</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.496187695289337</v>
       </c>
       <c r="E80">
-        <v>-18.4283779848517</v>
+        <v>-17.07835384215902</v>
       </c>
       <c r="F80">
-        <v>-1.849862185870001</v>
+        <v>-1.701465135862887</v>
       </c>
       <c r="G80">
-        <v>-7.427729823672908</v>
+        <v>-5.549786450520394</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.590025442783034</v>
       </c>
       <c r="E81">
-        <v>-19.05939366697652</v>
+        <v>-17.40019701835816</v>
       </c>
       <c r="F81">
-        <v>-2.24696246632182</v>
+        <v>-1.686421983828048</v>
       </c>
       <c r="G81">
-        <v>-6.241395829675078</v>
+        <v>-5.040674204763575</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.684252570803682</v>
       </c>
       <c r="E82">
-        <v>-19.51942322751972</v>
+        <v>-17.23992073780468</v>
       </c>
       <c r="F82">
-        <v>-2.27319686196848</v>
+        <v>-1.442719607394044</v>
       </c>
       <c r="G82">
-        <v>-6.987390850948907</v>
+        <v>-4.210756854069221</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.782020543258422</v>
       </c>
       <c r="E83">
-        <v>-20.49544523039291</v>
+        <v>-19.1654776990802</v>
       </c>
       <c r="F83">
-        <v>-2.651603375241323</v>
+        <v>-1.87686530646646</v>
       </c>
       <c r="G83">
-        <v>-7.273786145551258</v>
+        <v>-4.204046378261118</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.876252533731399</v>
       </c>
       <c r="E84">
-        <v>-21.3322528853223</v>
+        <v>-19.7202021795978</v>
       </c>
       <c r="F84">
-        <v>-3.086368693131032</v>
+        <v>-1.935946126368926</v>
       </c>
       <c r="G84">
-        <v>-7.055525188692648</v>
+        <v>-4.747359869984148</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.969543680975727</v>
       </c>
       <c r="E85">
-        <v>-21.42266839735945</v>
+        <v>-20.20666444292377</v>
       </c>
       <c r="F85">
-        <v>-2.574654670460471</v>
+        <v>-2.158961683652817</v>
       </c>
       <c r="G85">
-        <v>-5.697069311017031</v>
+        <v>-4.562889651444879</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.069744818700304</v>
       </c>
       <c r="E86">
-        <v>-22.6918502220672</v>
+        <v>-21.24588582904801</v>
       </c>
       <c r="F86">
-        <v>-2.692787317406305</v>
+        <v>-2.121393565201054</v>
       </c>
       <c r="G86">
-        <v>-6.519802777891167</v>
+        <v>-4.125079935512883</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.174439272967597</v>
       </c>
       <c r="E87">
-        <v>-25.68310655698981</v>
+        <v>-23.35210173238553</v>
       </c>
       <c r="F87">
-        <v>-3.07801792134341</v>
+        <v>-2.275232160677159</v>
       </c>
       <c r="G87">
-        <v>-6.181249838317599</v>
+        <v>-4.905392071846798</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.280006908311679</v>
       </c>
       <c r="E88">
-        <v>-26.16868123941027</v>
+        <v>-24.29403338292898</v>
       </c>
       <c r="F88">
-        <v>-3.657101408148849</v>
+        <v>-2.289243166928109</v>
       </c>
       <c r="G88">
-        <v>-7.304176953601767</v>
+        <v>-4.486713998586249</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.398532245074049</v>
       </c>
       <c r="E89">
-        <v>-27.21987591081079</v>
+        <v>-25.45997505720986</v>
       </c>
       <c r="F89">
-        <v>-3.097524316944533</v>
+        <v>-2.773977263289491</v>
       </c>
       <c r="G89">
-        <v>-6.017794962861624</v>
+        <v>-5.154063700029153</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.529997022042307</v>
       </c>
       <c r="E90">
-        <v>-26.89868936334276</v>
+        <v>-27.17993477006314</v>
       </c>
       <c r="F90">
-        <v>-3.092619553552557</v>
+        <v>-2.963005734403921</v>
       </c>
       <c r="G90">
-        <v>-6.973926862240692</v>
+        <v>-4.68130786538461</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.66572097389353</v>
       </c>
       <c r="E91">
-        <v>-27.70957603305225</v>
+        <v>-27.93928740556534</v>
       </c>
       <c r="F91">
-        <v>-3.336657418784694</v>
+        <v>-2.88801611853069</v>
       </c>
       <c r="G91">
-        <v>-7.073888784798985</v>
+        <v>-5.537381836384745</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.816323284162607</v>
       </c>
       <c r="E92">
-        <v>-31.73436372650846</v>
+        <v>-29.7624963257935</v>
       </c>
       <c r="F92">
-        <v>-3.753714726704758</v>
+        <v>-3.134370927388458</v>
       </c>
       <c r="G92">
-        <v>-7.505299216203571</v>
+        <v>-5.801553438781968</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.982599379896653</v>
       </c>
       <c r="E93">
-        <v>-33.0831855593521</v>
+        <v>-31.99027005691892</v>
       </c>
       <c r="F93">
-        <v>-3.941249651391941</v>
+        <v>-3.409238142250584</v>
       </c>
       <c r="G93">
-        <v>-6.487266736331209</v>
+        <v>-5.826316319415717</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.150470238690041</v>
       </c>
       <c r="E94">
-        <v>-35.624737254469</v>
+        <v>-33.38715711287998</v>
       </c>
       <c r="F94">
-        <v>-3.441384596051024</v>
+        <v>-2.881452135230907</v>
       </c>
       <c r="G94">
-        <v>-8.265758010938477</v>
+        <v>-6.017924074137655</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.324020565521176</v>
       </c>
       <c r="E95">
-        <v>-35.48256581299819</v>
+        <v>-35.28779161745428</v>
       </c>
       <c r="F95">
-        <v>-3.75320031054762</v>
+        <v>-3.341132259494617</v>
       </c>
       <c r="G95">
-        <v>-8.505822220718727</v>
+        <v>-6.415318650126228</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.501111340231558</v>
       </c>
       <c r="E96">
-        <v>-37.27235233081274</v>
+        <v>-37.99283933814411</v>
       </c>
       <c r="F96">
-        <v>-4.163340750654308</v>
+        <v>-3.673702719268354</v>
       </c>
       <c r="G96">
-        <v>-8.409885921536187</v>
+        <v>-6.123427849928689</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.665202711490757</v>
       </c>
       <c r="E97">
-        <v>-39.80992123303989</v>
+        <v>-40.02758460045557</v>
       </c>
       <c r="F97">
-        <v>-4.281568659851465</v>
+        <v>-3.58589991640862</v>
       </c>
       <c r="G97">
-        <v>-8.712420125642485</v>
+        <v>-5.902412519181405</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.807920631110489</v>
       </c>
       <c r="E98">
-        <v>-40.82911544286521</v>
+        <v>-41.29376631113324</v>
       </c>
       <c r="F98">
-        <v>-4.806039540525139</v>
+        <v>-3.67804253609162</v>
       </c>
       <c r="G98">
-        <v>-8.975472763647433</v>
+        <v>-6.954735629749536</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.924408070458465</v>
       </c>
       <c r="E99">
-        <v>-44.40031306581712</v>
+        <v>-44.1476717651662</v>
       </c>
       <c r="F99">
-        <v>-4.908371079262572</v>
+        <v>-4.059251416288133</v>
       </c>
       <c r="G99">
-        <v>-8.598845239826709</v>
+        <v>-7.821916481033928</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.00103555276425</v>
       </c>
       <c r="E100">
-        <v>-46.35913846139</v>
+        <v>-45.91493591750361</v>
       </c>
       <c r="F100">
-        <v>-4.728578076321954</v>
+        <v>-3.924651653742047</v>
       </c>
       <c r="G100">
-        <v>-9.787830980801495</v>
+        <v>-7.905226359529688</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.0176072221535</v>
       </c>
       <c r="E101">
-        <v>-47.64144833224598</v>
+        <v>-48.1079241755391</v>
       </c>
       <c r="F101">
-        <v>-4.524987734633711</v>
+        <v>-3.517082466053649</v>
       </c>
       <c r="G101">
-        <v>-8.760929549429425</v>
+        <v>-7.664976759199238</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.980853586973469</v>
       </c>
       <c r="E102">
-        <v>-50.80148881826398</v>
+        <v>-49.65755665977888</v>
       </c>
       <c r="F102">
-        <v>-5.020671191325296</v>
+        <v>-4.376113545002584</v>
       </c>
       <c r="G102">
-        <v>-9.774300781182493</v>
+        <v>-8.185983795078659</v>
       </c>
     </row>
   </sheetData>
